--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2018_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supneta_a_2018_maule.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:49</t>
+    <t xml:space="preserve">2026-09-24 00:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -669,10 +669,10 @@
         <v>30</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0.45</v>
@@ -695,10 +695,10 @@
         <v>-0.38</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="10">
@@ -718,7 +718,7 @@
         <v>-0.04</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.33</v>
@@ -741,10 +741,10 @@
         <v>0.15</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="12">
